--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43664-2025 artfynd.xlsx
+++ b/artfynd/A 43664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339683</v>
       </c>
       <c r="B2" t="n">
-        <v>78881</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339684</v>
       </c>
       <c r="B3" t="n">
-        <v>78882</v>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
